--- a/planificador.xlsx
+++ b/planificador.xlsx
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Lunes 26/08/2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9:00</t>
+          <t>7:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DORMIR (Notif. 10:45)</t>
+          <t>GUITARRA</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#ffa500</t>
+          <t>#ff0000</t>
         </is>
       </c>
     </row>
